--- a/database_guru.xlsx
+++ b/database_guru.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SMK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SMK\DATA APLIKASI\sistem-izin-smk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14827EE7-ABD8-4DF3-BA60-7BD48D00C9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043F387-785F-4B23-9A2F-808D11BF7E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{D12AF689-9614-46F1-B931-E13F937DBFA9}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="60">
-  <si>
-    <t>JOKO SUSILO, S.Pd</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>TITIN PUSPITA SARI HUTAPEA,S.Pd</t>
   </si>
@@ -277,11 +274,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -618,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1397668B-9CD0-45D8-AA83-B763892591EE}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.7265625" bestFit="1" customWidth="1"/>
@@ -629,44 +623,44 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>28</v>
-      </c>
       <c r="D1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1">
-        <v>13509</v>
+      <c r="B2" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>85230950381</v>
+        <v>85249531492</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>82155138864</v>
+        <v>85654271885</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
@@ -677,52 +671,52 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>85654271885</v>
+        <v>81257615088</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>81257615088</v>
+        <v>85787701561</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>85787701561</v>
+        <v>82158783400</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>82158783400</v>
+        <v>82149879510</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
@@ -733,287 +727,273 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>82149879510</v>
+        <v>85742221915</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9">
-        <v>85742221915</v>
+        <v>82252352472</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10">
-        <v>82252352472</v>
+        <v>81554437802</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11">
-        <v>81554437802</v>
+        <v>82154159105</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12">
-        <v>82154159105</v>
+        <v>85821897452</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13">
-        <v>85821897452</v>
+        <v>82256598276</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D14">
-        <v>82256598276</v>
+        <v>85651121418</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>51</v>
+      <c r="B15" s="3">
+        <v>25690</v>
       </c>
       <c r="C15" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>85651121418</v>
+        <v>85895042030</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="4">
-        <v>25690</v>
+      <c r="B16" s="3">
+        <v>24057</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16">
-        <v>85895042030</v>
+        <v>81270452172</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="4">
-        <v>24057</v>
+      <c r="B17" s="3">
+        <v>26111</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17">
-        <v>81270452172</v>
+        <v>89505774201</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="4">
-        <v>26111</v>
+      <c r="B18" s="3">
+        <v>26246</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18">
-        <v>89505774201</v>
+        <v>85822093461</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4">
-        <v>26246</v>
+      <c r="B19" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D19">
-        <v>85822093461</v>
+        <v>82250455464</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D20">
-        <v>82250455464</v>
+        <v>82226182628</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>53</v>
+      <c r="B21" s="5">
+        <v>25.286000000000001</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D21">
-        <v>82226182628</v>
+        <v>85134615905</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="6">
-        <v>25.286000000000001</v>
+      <c r="B22" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D22">
-        <v>85134615905</v>
+        <v>81545332722</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23">
-        <v>81545332722</v>
+        <v>83106618348</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>55</v>
-      </c>
+      <c r="B24" s="7"/>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D24">
-        <v>83106618348</v>
+        <v>85845230859</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>23</v>
       </c>
-      <c r="B25" s="8"/>
+      <c r="B25" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D25">
-        <v>85845230859</v>
+        <v>85753591537</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D26">
-        <v>85753591537</v>
+        <v>82124431574</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D27">
-        <v>82124431574</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28">
         <v>89652859749</v>
       </c>
     </row>

--- a/database_guru.xlsx
+++ b/database_guru.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SMK\DATA APLIKASI\sistem-izin-smk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6043F387-785F-4B23-9A2F-808D11BF7E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C09FEA31-4CF7-46B7-BA47-A8241C492FF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{D12AF689-9614-46F1-B931-E13F937DBFA9}"/>
   </bookViews>
